--- a/public/data/menu.xlsx
+++ b/public/data/menu.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="363">
   <si>
     <t>Category</t>
   </si>
@@ -54,7 +54,7 @@
     <t>special</t>
   </si>
   <si>
-    <t>Mì ramen</t>
+    <t>Mì ramen ( khô và nước )</t>
   </si>
   <si>
     <t>mỳ ramen, nước dùng</t>
@@ -63,126 +63,129 @@
     <t>vegan ramen ( dry / soup )</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325976/M%C3%AC_ramen_monchinh_dnqjwy.png</t>
+  </si>
+  <si>
+    <t>Nấm xúc bánh đa</t>
+  </si>
+  <si>
+    <t>nấm, bánh đa, gia vị</t>
+  </si>
+  <si>
+    <t>Stir-fried Mushrooms served with Sesame Rice Crackers</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325988/N%E1%BA%A5m_x%C3%BAc_b%C3%A1nh_%C4%91a_monkhaivi_sriwx7.png</t>
+  </si>
+  <si>
+    <t>ĐẬU HŨ NON CHIÊN GIÒN CHÀ BÔNG</t>
+  </si>
+  <si>
+    <t>đậu hủ non, chà bông chay, rong biển, mỡ hành dùng kèm với mayonnaise tương ớt</t>
+  </si>
+  <si>
+    <t>Fried Young Tofu with Meat floss</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151896/IMG_3758_mdxtav.jpg</t>
+  </si>
+  <si>
+    <t>NẤM bào ngư xốc muối hongkong</t>
+  </si>
+  <si>
+    <t>nấm bào ngư, muối Hong Kong dùng kèm với mayonnaise tương ớt</t>
+  </si>
+  <si>
+    <t>HongKong Salted Oyster Mushrooms</t>
+  </si>
+  <si>
+    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/dacbiet%2FNa%CC%82%CC%81m%20ba%CC%80o%20ngu%CC%9B%20xo%CC%82%CC%81c%20muo%CC%82%CC%81i%20HongKong_dacbiet.jpg?alt=media&amp;token=7158a1fe-cd82-4452-a322-31ac284da192</t>
+  </si>
+  <si>
+    <t>ĐẬU NON RONG BIỂN SỐT TERIYAKI</t>
+  </si>
+  <si>
+    <t>đậu hủ non cuộn rong biển chiên giòn, sốt teriyaki</t>
+  </si>
+  <si>
+    <t>Seaweed rolled Young Tofu &amp; Teriyaki Sauce</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151906/IMG_3883_ip1sfc.jpg</t>
+  </si>
+  <si>
+    <t>KHOAI TÂY BỌT BIỂN</t>
+  </si>
+  <si>
+    <t>khoai tây , chà bông chay , rong biển dùng với mayonnaise tương ớt</t>
+  </si>
+  <si>
+    <t>spongy spongy potato</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151897/IMG_3736_ayg9jn.jpg</t>
+  </si>
+  <si>
+    <t>salad</t>
+  </si>
+  <si>
+    <t>GỎI NẤM BÀO NGƯ XÉ TRỘN</t>
+  </si>
+  <si>
+    <t>nấm bào ngư, tàu hủ ki, rau thơm các loại, xốt gỏi chua cay</t>
+  </si>
+  <si>
+    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20na%CC%82%CC%81m%20ba%CC%80o%20ngu%CC%9B%20xe%CC%81%20tro%CC%A3%CC%82n_%20khaivi.jpg?alt=media&amp;token=afb1b5fc-4db0-4562-88cd-75c1ddc67200</t>
+  </si>
+  <si>
+    <t>GỎI somtum thái lan</t>
+  </si>
+  <si>
+    <t>xoài, cà rốt, đu dủ, cà chua, cà pháo, đậu đũa, tắc, lá chanh, ngò gai, xốt Thái</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thailand Somtum Salad </t>
+  </si>
+  <si>
+    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20Somtum%20Tha%CC%81i%20Lan_khaivi.jpg?alt=media&amp;token=1be1b1ea-7c94-466f-b67b-194d9f9b13ac</t>
+  </si>
+  <si>
+    <t>gỎI NGÓ SEN</t>
+  </si>
+  <si>
+    <t>ngó sen, dưa leo, cà rốt, tàu hũ ki, rau thơm các loại, xốt gỏi chua cay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotus Delight Salad </t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151915/IMG_4017_cp8wde.jpg</t>
+  </si>
+  <si>
+    <t>GỎI RONG SỤN</t>
+  </si>
+  <si>
+    <t>rong sụn, dưa leo, cà rốt, rau thơm các loại, xốt gỏi chua cay</t>
+  </si>
+  <si>
+    <t>Cartilage Algae Salad</t>
+  </si>
+  <si>
+    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20rong%20su%CC%A3n_khaivi.jpg?alt=media&amp;token=5b7e2fcb-8602-40ec-85c0-22c4942a48ef</t>
+  </si>
+  <si>
+    <t>SALAD Trái cây NHIỆT ĐỚi</t>
+  </si>
+  <si>
+    <t>rau xà lách, cà chua, thanh long, thơm, bắp Mỹ, cam, nho khô, xốt chanh dây</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tropical Fruity Salad </t>
+  </si>
+  <si>
     <t>https://res.cloudinary.com/dix539uvo/image/upload/v1775977936/salad-rau_vyjipw.jpg</t>
   </si>
   <si>
-    <t>Nấm xúc bánh đa</t>
-  </si>
-  <si>
-    <t>nấm, bánh đa, gia vị</t>
-  </si>
-  <si>
-    <t>Stir-fried Mushrooms served with Sesame Rice Crackers</t>
-  </si>
-  <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FNa%CC%82%CC%81m%20xu%CC%81c%20ba%CC%81nh%20%C4%91a_monkhaivi.jpg?alt=media&amp;token=efc9ec85-3da1-42b0-a0f6-c8c1d5147086</t>
-  </si>
-  <si>
-    <t>ĐẬU HŨ NON CHIÊN GIÒN CHÀ BÔNG</t>
-  </si>
-  <si>
-    <t>đậu hủ non, chà bông chay, rong biển, mỡ hành dùng kèm với mayonnaise tương ớt</t>
-  </si>
-  <si>
-    <t>Fried Young Tofu with Meat floss</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151896/IMG_3758_mdxtav.jpg</t>
-  </si>
-  <si>
-    <t>NẤM bào ngư xốc muối hongkong</t>
-  </si>
-  <si>
-    <t>nấm bào ngư, muối Hong Kong dùng kèm với mayonnaise tương ớt</t>
-  </si>
-  <si>
-    <t>HongKong Salted Oyster Mushrooms</t>
-  </si>
-  <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/dacbiet%2FNa%CC%82%CC%81m%20ba%CC%80o%20ngu%CC%9B%20xo%CC%82%CC%81c%20muo%CC%82%CC%81i%20HongKong_dacbiet.jpg?alt=media&amp;token=7158a1fe-cd82-4452-a322-31ac284da192</t>
-  </si>
-  <si>
-    <t>ĐẬU NON RONG BIỂN SỐT TERIYAKI</t>
-  </si>
-  <si>
-    <t>đậu hủ non cuộn rong biển chiên giòn, sốt teriyaki</t>
-  </si>
-  <si>
-    <t>Seaweed rolled Young Tofu &amp; Teriyaki Sauce</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151906/IMG_3883_ip1sfc.jpg</t>
-  </si>
-  <si>
-    <t>KHOAI TÂY BỌT BIỂN</t>
-  </si>
-  <si>
-    <t>khoai tây , chà bông chay , rong biển dùng với mayonnaise tương ớt</t>
-  </si>
-  <si>
-    <t>spongy spongy potato</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151897/IMG_3736_ayg9jn.jpg</t>
-  </si>
-  <si>
-    <t>salad</t>
-  </si>
-  <si>
-    <t>GỎI NẤM BÀO NGƯ XÉ TRỘN</t>
-  </si>
-  <si>
-    <t>nấm bào ngư, tàu hủ ki, rau thơm các loại, xốt gỏi chua cay</t>
-  </si>
-  <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20na%CC%82%CC%81m%20ba%CC%80o%20ngu%CC%9B%20xe%CC%81%20tro%CC%A3%CC%82n_%20khaivi.jpg?alt=media&amp;token=afb1b5fc-4db0-4562-88cd-75c1ddc67200</t>
-  </si>
-  <si>
-    <t>GỎI somtum thái lan</t>
-  </si>
-  <si>
-    <t>xoài, cà rốt, đu dủ, cà chua, cà pháo, đậu đũa, tắc, lá chanh, ngò gai, xốt Thái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thailand Somtum Salad </t>
-  </si>
-  <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20Somtum%20Tha%CC%81i%20Lan_khaivi.jpg?alt=media&amp;token=1be1b1ea-7c94-466f-b67b-194d9f9b13ac</t>
-  </si>
-  <si>
-    <t>gỎI NGÓ SEN</t>
-  </si>
-  <si>
-    <t>ngó sen, dưa leo, cà rốt, tàu hũ ki, rau thơm các loại, xốt gỏi chua cay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lotus Delight Salad </t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151915/IMG_4017_cp8wde.jpg</t>
-  </si>
-  <si>
-    <t>GỎI RONG SỤN</t>
-  </si>
-  <si>
-    <t>rong sụn, dưa leo, cà rốt, rau thơm các loại, xốt gỏi chua cay</t>
-  </si>
-  <si>
-    <t>Cartilage Algae Salad</t>
-  </si>
-  <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20rong%20su%CC%A3n_khaivi.jpg?alt=media&amp;token=5b7e2fcb-8602-40ec-85c0-22c4942a48ef</t>
-  </si>
-  <si>
-    <t>SALAD Trái cây NHIỆT ĐỚi</t>
-  </si>
-  <si>
-    <t>rau xà lách, cà chua, thanh long, thơm, bắp Mỹ, cam, nho khô, xốt chanh dây</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tropical Fruity Salad </t>
-  </si>
-  <si>
     <t>SALAD rong biển nhật</t>
   </si>
   <si>
@@ -255,7 +258,7 @@
     <t>Vietnamese Pancake</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncuon%2FBa%CC%81nh%20xe%CC%80o_moncuon.jpg?alt=media&amp;token=7425fff4-9c1c-4105-95c2-379f5bce4f53</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325852/B%C3%A1nh_x%C3%A8o_moncuon_jw9jjp.png</t>
   </si>
   <si>
     <t>Nấm nướng lá lốt</t>
@@ -294,7 +297,7 @@
     <t>Thai hotpot</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monlau%2FLa%CC%82%CC%89u%20Tha%CC%81i_monlau(1).jpg?alt=media&amp;token=36cd92a3-3e5b-4d92-9b2a-7a12a5ccc377</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325867/L%E1%BA%A9u_Th%C3%A1i_monlau_1_jrs05t.png</t>
   </si>
   <si>
     <t>lẩu sa tế diệu thiện</t>
@@ -306,7 +309,7 @@
     <t>"Dieu Thien" spicy sauce hotpot</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monlau%2FLa%CC%82%CC%89u%20sa%20te%CC%82%CC%81%20Die%CC%A3%CC%82u%20Thie%CC%A3%CC%82n_monlau(1).jpg?alt=media&amp;token=fb819ffd-ad81-4e22-b5d6-63c322b2e3ec</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325952/L%E1%BA%A9u_sa_t%E1%BA%BF_Di%E1%BB%87u_Thi%E1%BB%87n_monlau_1_wkjfs9.png</t>
   </si>
   <si>
     <t>lẩu chao</t>
@@ -342,7 +345,7 @@
     <t>lovebird hotpot</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monlau%2FLa%CC%82%CC%89u%20uye%CC%82n%20u%CC%9Bo%CC%9Bng_monlau.jpg?alt=media&amp;token=11819106-1900-4f9f-95eb-00406bc6f65d</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325969/L%E1%BA%A9u_uy%C3%AAn_%C6%B0%C6%A1ng_monlau_tasirl.png</t>
   </si>
   <si>
     <t>mainDish</t>
@@ -474,7 +477,7 @@
     <t>nấm, khoai tây</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monchinh%2FNa%CC%82%CC%81m%20lu%CC%81c%20la%CC%86%CC%81c-khoai%20ta%CC%82y_monchinh.JPG?alt=media&amp;token=f7791b30-7bfa-4b02-860c-528b01a2a6b8</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325929/N%E1%BA%A5m_l%C3%BAc_l%E1%BA%AFc-khoai_t%C3%A2y_monchinh_fi29of.jpg</t>
   </si>
   <si>
     <t>soup</t>
@@ -489,7 +492,7 @@
     <t>Seaweed Soup with Tofu &amp; Mushrooms</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncanh%2FCanh%20na%CC%82%CC%81m%20ta%CC%80u%20hu%CC%83%20rong%20bie%CC%82%CC%89n_moncanh.jpg?alt=media&amp;token=3ff3a3e5-f700-4c64-8f20-34e4405516c3</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325975/Canh_n%E1%BA%A5m_t%C3%A0u_h%C5%A9_rong_bi%E1%BB%83n_moncanh-sup_uynxis.jpg</t>
   </si>
   <si>
     <t>CANH CHUA NAM BỘ</t>
@@ -600,7 +603,7 @@
     <t>Bok-choy with Shiitake Sauce</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151902/IMG_3819_kma4oc.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325910/C%E1%BA%A3i_th%C3%ACa_s%E1%BB%91t_n%E1%BA%A5m_%C4%91%C3%B4ng_c%C3%B4_monman_mirtvr.jpg</t>
   </si>
   <si>
     <t>NẤM SỐT TIÊU ĐEN</t>
@@ -666,6 +669,9 @@
     <t>Braised Mushroom with Ginger</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325924/Ch%C3%A2n_n%E1%BA%A5m_kho_g%E1%BB%ABng_monman3871_wx1ylw.jpg</t>
+  </si>
+  <si>
     <t>dessert</t>
   </si>
   <si>
@@ -678,7 +684,7 @@
     <t>Gum Tragacanth Refresh Beauty Sweet Soup</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151909/IMG_3970_ehrvcj.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325938/Ch%C3%A8_tuy%E1%BA%BFt_y%E1%BA%BFn_d%C6%B0%E1%BB%A1ng_nhan_trangmieng_kqi251.png</t>
   </si>
   <si>
     <t>Chè hạt sen đông trùng hạ thảo</t>
@@ -690,7 +696,7 @@
     <t>Lotus Seed Sweet Soup with Cordyceps</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/trangmieng%2FChe%CC%80%20ha%CC%A3t%20sen%20%C4%91o%CC%82ng%20tru%CC%80ng%20ha%CC%A3%20tha%CC%89o_trangmieng.jpg?alt=media&amp;token=e55222b8-7b14-41d1-9d32-69b53b8ce267</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325935/Ch%C3%A8_h%E1%BA%A1t_sen_%C4%91%C3%B4ng_tr%C3%B9ng_h%E1%BA%A1_th%E1%BA%A3o_trangmieng_v3wb22.png</t>
   </si>
   <si>
     <t>Sữa chua dâu tằm</t>
@@ -702,7 +708,7 @@
     <t>Mulberry Yogurt</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151908/IMG_3954_nyczae.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325891/S%E1%BB%AFa_chua_d%C3%A2u_t%E1%BA%B1m_trangmieng_dngnth.jpg</t>
   </si>
   <si>
     <t>Panna Cotta (Việt quất, chanh dây, ổi, đào, dâu tằm)</t>
@@ -732,7 +738,7 @@
     <t>daisies , rose, Goji berries , Apple , sugar , Cordyceps (can be used hot or cold)</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trasangtao%2FTra%CC%80%20tha%CC%89o%20mo%CC%A3%CC%82c_trasangtao.JPG?alt=media&amp;token=5c3c14e0-f95d-4fe6-9512-dd21a30073aa</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325945/Tr%C3%A0_th%E1%BA%A3o_m%E1%BB%99c_trasangtao_pvaku6.jpg</t>
   </si>
   <si>
     <t>TRÀ ĐÀO CAM SẢ</t>
@@ -747,7 +753,7 @@
     <t>crushed lemongrass, peach tea , peach syrup , peach jam , kumquat juice ,sliced peach</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trasangtao%2FTra%CC%80%20%C4%91a%CC%80o%20cam%20sa%CC%89_trasangtao.JPG?alt=media&amp;token=304c914f-9aaf-4be4-b833-40e5a5ec5bd1</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325873/Tr%C3%A0_%C4%91%C3%A0o_cam_s%E1%BA%A3_trasangtao_exv4fk.jpg</t>
   </si>
   <si>
     <t>TRÀ LÀI LỆ CHI</t>
@@ -762,7 +768,7 @@
     <t>Lychee syrup , fresh lychee</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trasangtao%2FTra%CC%80%20la%CC%80i%20le%CC%A3%CC%82%20chi_trasangtao.JPG?alt=media&amp;token=7e11fc08-31b8-4190-a6d0-d4b30f58a687</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325893/Tr%C3%A0_l%C3%A0i_l%E1%BB%87_chi_trasangtao_rysrnm.jpg</t>
   </si>
   <si>
     <t>TRÀ ỔI HỒNG</t>
@@ -777,7 +783,7 @@
     <t>kumquat juice , guava jam , guava syrup, fresh guava</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trasangtao%2FTra%CC%80%20o%CC%82%CC%89i%20ho%CC%82%CC%80ng_trasangtao.JPG?alt=media&amp;token=3333eb63-9ab5-43dc-8fae-8fa27f4ce823</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325881/Tr%C3%A0_%E1%BB%95i_h%E1%BB%93ng_trasangtao_wmmicw.jpg</t>
   </si>
   <si>
     <t>TRÀ GỪNG MẬT ONG</t>
@@ -792,7 +798,7 @@
     <t>ginger tea , honey , sliced ginger</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trasangtao%2FTra%CC%80%20gu%CC%9B%CC%80ng%20ma%CC%A3%CC%82t%20ong_trasangtao.JPG?alt=media&amp;token=0390f4aa-02a4-4d1a-9cc0-70b2f648bb41</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325923/Tr%C3%A0_g%E1%BB%ABng_m%E1%BA%ADt_ong_trasangtao_fpdkuv.jpg</t>
   </si>
   <si>
     <t>TRÀ TẮC XÍ MUỘI</t>
@@ -807,7 +813,7 @@
     <t>soot , lipton tea , kumquat juice , Kumquat Marmalade</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trasangtao%2FTra%CC%80%20ta%CC%86%CC%81c%20xi%CC%81%20muo%CC%A3%CC%82i_trasangtao.JPG?alt=media&amp;token=08ed6df7-0383-4921-9140-b0cda52c14f5</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325888/Tr%C3%A0_t%E1%BA%AFc_x%C3%AD_mu%E1%BB%99i_trasangtao_hurnp9.jpg</t>
   </si>
   <si>
     <t>TRÀ LÀI HẠT ĐÁC</t>
@@ -822,7 +828,7 @@
     <t>pineapple juice added with arenga pinnata</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trasangtao%2FTra%CC%80%20la%CC%80i%20ha%CC%A3t%20%C4%91a%CC%81c_trasangtao.JPG?alt=media&amp;token=9307f7d8-e258-4105-be6e-ff60a7174fb1</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325926/Tr%C3%A0_l%C3%A0i_h%E1%BA%A1t_%C4%91%C3%A1c_trasangtao_p9smi5.jpg</t>
   </si>
   <si>
     <t>juice</t>
@@ -840,7 +846,7 @@
     <t>pineapple juice</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_nuocep%2Fthomep_nuocep.jpg?alt=media&amp;token=6de3e059-83e3-40f2-9290-f74289212e99</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326551/Th%C6%A1mep_hom2ry.jpg</t>
   </si>
   <si>
     <t>cam ép</t>
@@ -855,7 +861,7 @@
     <t>orange juice</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_nuocep%2Fnuoc-ep-cam-tuoi-thom-ngon-tai-nha.jpg?alt=media&amp;token=67b7bf76-20fa-4a61-942b-8597afbeb776</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326550/camep_xlfuo2.jpg</t>
   </si>
   <si>
     <t>dưa hấu</t>
@@ -870,7 +876,7 @@
     <t>watermelon juice</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_nuocep%2Fduahau_nuocep%202.jpg?alt=media&amp;token=366c2c11-53dd-4b3c-a7a0-5fd9f4ece395</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326550/duahau_jgctft.jpg</t>
   </si>
   <si>
     <t>chanh dây</t>
@@ -885,7 +891,7 @@
     <t>Passion fruit juice, passion fruit syrup, passion fruit jam</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_nuocep%2Fchanhday_nuocep.jpg?alt=media&amp;token=39578f10-f292-45e2-9ea1-9b9a60a9e554</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326550/chanhday_bry0vw.jpg</t>
   </si>
   <si>
     <t>Cam cà rốt</t>
@@ -897,7 +903,7 @@
     <t>Orange Carrot</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_nuocep%2Fparadigm-visuals-Tl_YI6wdNIE-unsplash.jpg?alt=media&amp;token=a14c1c4c-e132-4563-bb6d-2f96c8d636d4</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326549/camcarot_mlqaxx.jpg</t>
   </si>
   <si>
     <t>Thơm cà rốt</t>
@@ -912,7 +918,7 @@
     <t>mix pineapple juice and carrot juice</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_nuocep%2FIMG_5212.jpeg?alt=media&amp;token=040bbd7b-6c31-4397-add7-292d127bbcce</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326637/thomcarot1_pylxs5.jpg</t>
   </si>
   <si>
     <t>soda</t>
@@ -930,7 +936,7 @@
     <t>blue sea serum, mint serum, lemon juice, 1-2 crushed mint leaves, soda</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_soda%2FSoda%20Bie%CC%82%CC%89n%20xanh_soda.jpg?alt=media&amp;token=cfa0b542-efbd-459d-8bc4-1c6c43447b2f</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325980/Soda_Bi%E1%BB%83n_xanh_soda_f4kydh.png</t>
   </si>
   <si>
     <t>Soda Chanh dây nhiệt đới</t>
@@ -945,7 +951,7 @@
     <t>passion fruit serum, passion fruit syrup, soda</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_soda%2FSoda%20Chanh%20da%CC%82y_soda.jpg?alt=media&amp;token=6d80ab54-7a51-4f08-be6f-884605b1b178</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325992/Soda_Chanh_d%C3%A2y_soda_mszjus.png</t>
   </si>
   <si>
     <t>Soda Chanh tươi</t>
@@ -960,7 +966,7 @@
     <t>fresh lemon juice, sugar serum, soda</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_soda%2FSoda%20Chanh%20tu%CC%9Bo%CC%9Bi_soda.jpg?alt=media&amp;token=df5eccd2-5139-4157-90ac-ebc1f669cdff</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325988/Soda_Chanh_t%C6%B0%C6%A1i_soda_or3jrz.png</t>
   </si>
   <si>
     <t>Soda Việt quất</t>
@@ -975,7 +981,7 @@
     <t>blueberry juice, sugar serum, soda</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_soda%2FSoda%20Vie%CC%A3%CC%82t%20qua%CC%82%CC%81t_Soda.jpg?alt=media&amp;token=8e6507ad-71a2-42fb-92a6-ab76677c9f5e</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325990/Soda_Vi%E1%BB%87t_qu%E1%BA%A5t_Soda_fkftwl.png</t>
   </si>
   <si>
     <t>thaiTea</t>
@@ -987,7 +993,7 @@
     <t>Thai Green Milk Tea</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trathai%2FTra%CC%80%20su%CC%9B%CC%83a%20Tha%CC%81i%20xanh_trathai.JPG?alt=media&amp;token=f3e3584a-9151-4d09-99e4-bf7c24295e76</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325929/Tr%C3%A0_s%E1%BB%AFa_Th%C3%A1i_xanh_trathai_jso0yy.jpg</t>
   </si>
   <si>
     <t>Trà Thái xanh chanh mật ong</t>
@@ -996,7 +1002,7 @@
     <t>Thai green tea with lemon and honey</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/nuoc_trathai%2FTra%CC%80%20Tha%CC%81i%20xanh%20chanh%20ma%CC%A3%CC%82t%20ong_trathai.JPG?alt=media&amp;token=1a479f2b-2d4d-4076-a70f-45e8bdc00714</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780325996/Tr%C3%A0_Th%C3%A1i_xanh_chanh_m%E1%BA%ADt_ong_trathai_kerx8n.jpg</t>
   </si>
   <si>
     <t>coffee</t>
@@ -1109,7 +1115,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$đ-42A]"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot;₫&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1170,11 +1176,6 @@
       <sz val="9.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;Google Sans Mono&quot;"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -1255,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1342,28 +1343,25 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
@@ -2129,7 +2127,7 @@
         <v>生菜、西红柿、火龙果、菠萝、甜玉米、橙子、葡萄干、百香果酱</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J12" s="10" t="b">
         <v>0</v>
@@ -2147,16 +2145,16 @@
         <v>36</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="7">
         <v>59000.0</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D13&lt;&gt;"""", GOOGLETRANSLATE(D13, ""vi"", ""en""), """")
@@ -2173,7 +2171,7 @@
         <v>日本海带、甜椒、生菜、烤芝麻酱</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J13" s="10" t="b">
         <v>0</v>
@@ -2188,19 +2186,19 @@
     </row>
     <row r="14" ht="36.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="7">
         <v>50000.0</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D14&lt;&gt;"""", GOOGLETRANSLATE(D14, ""vi"", ""en""), """")
@@ -2217,7 +2215,7 @@
         <v>馅料包括各种土豆、胡萝卜、木耳、玉米和绿豆，佐以酸甜鱼露。</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J14" s="10" t="b">
         <v>0</v>
@@ -2232,19 +2230,19 @@
     </row>
     <row r="15" ht="36.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" s="7">
         <v>50000.0</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D15&lt;&gt;"""", GOOGLETRANSLATE(D15, ""vi"", ""en""), """")
@@ -2261,7 +2259,7 @@
         <v>新鲜米粉、各种香草、炒什锦蘑菇，佐以花生酱。</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J15" s="10" t="b">
         <v>1</v>
@@ -2276,19 +2274,19 @@
     </row>
     <row r="16" ht="36.75" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="7">
         <v>50000.0</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D16&lt;&gt;"""", GOOGLETRANSLATE(D16, ""vi"", ""en""), """")
@@ -2305,7 +2303,7 @@
         <v>各种红薯馅料、烤米粉、粉丝、各种香草，佐以糖醋鱼露。</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16" s="10" t="b">
         <v>0</v>
@@ -2320,19 +2318,19 @@
     </row>
     <row r="17" ht="36.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" s="7">
         <v>55000.0</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D17&lt;&gt;"""", GOOGLETRANSLATE(D17, ""vi"", ""en""), """")
@@ -2349,7 +2347,7 @@
         <v>米纸卷，内含新鲜粉丝、各种生蔬菜、蚝油蘑菇和花生酱。</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J17" s="10" t="b">
         <v>0</v>
@@ -2364,19 +2362,19 @@
     </row>
     <row r="18" ht="36.75" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="7">
         <v>59000.0</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D18&lt;&gt;"""", GOOGLETRANSLATE(D18, ""vi"", ""en""), """")
@@ -2393,7 +2391,7 @@
         <v>馅料包括豆芽、胡萝卜、炒什锦蘑菇和绿豆，用米纸包裹着各种新鲜蔬菜，佐以糖醋鱼露。</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J18" s="10" t="b">
         <v>0</v>
@@ -2408,19 +2406,19 @@
     </row>
     <row r="19" ht="36.75" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="7">
         <v>55000.0</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D19&lt;&gt;"""", GOOGLETRANSLATE(D19, ""vi"", ""en""), """")
@@ -2437,7 +2435,7 @@
         <v>烤什锦炒蘑菇，用槟榔叶包裹，配米粉、各种新鲜蔬菜和素菜蘸酱。</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J19" s="10" t="b">
         <v>0</v>
@@ -2452,19 +2450,19 @@
     </row>
     <row r="20" ht="36.75" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" s="7">
         <v>150000.0</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D20&lt;&gt;"""", GOOGLETRANSLATE(D20, ""vi"", ""en""), """")
@@ -2481,7 +2479,7 @@
         <v>青花椒汤底，菠菜，大白菜，芥菜，杏鲍菇，平菇，金针菇，嫩豆腐，佐以素鱼露和新鲜米粉。</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J20" s="10" t="b">
         <v>0</v>
@@ -2496,19 +2494,19 @@
     </row>
     <row r="21" ht="36.75" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" s="7">
         <v>150000.0</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D21&lt;&gt;"""", GOOGLETRANSLATE(D21, ""vi"", ""en""), """")
@@ -2525,7 +2523,7 @@
         <v>泰式火锅汤底，香蕉花，大白菜，空心菜，水芹，杏鲍菇，金针菇，平菇，嫩豆腐，佐以素鱼露和新鲜米粉。</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" s="10" t="b">
         <v>0</v>
@@ -2540,19 +2538,19 @@
     </row>
     <row r="22" ht="36.75" customHeight="1">
       <c r="A22" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" s="7">
         <v>150000.0</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D22&lt;&gt;"""", GOOGLETRANSLATE(D22, ""vi"", ""en""), """")
@@ -2569,7 +2567,7 @@
         <v>沙爹火锅汤底，菠菜，大白菜，平菇，杏鲍菇，黑金针菇，豆腐，豆腐皮，佐以沙爹鱼露和新鲜米粉。</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J22" s="15" t="b">
         <v>0</v>
@@ -2584,19 +2582,19 @@
     </row>
     <row r="23" ht="36.75" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" s="7">
         <v>150000.0</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F23" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D23&lt;&gt;"""", GOOGLETRANSLATE(D23, ""vi"", ""en""), """")
@@ -2613,7 +2611,7 @@
         <v>发酵豆腐汤、菠菜、大白菜、芥菜、杏鲍菇、平菇和豆腐皮，配以素食发酵豆腐蘸酱和新鲜米粉。</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J23" s="10" t="b">
         <v>0</v>
@@ -2628,19 +2626,19 @@
     </row>
     <row r="24" ht="36.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="7">
         <v>150000.0</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D24&lt;&gt;"""", GOOGLETRANSLATE(D24, ""vi"", ""en""), """")
@@ -2657,7 +2655,7 @@
         <v>泡菜火锅汤底，配紫甘蓝、大白菜、平菇和韩式面条。</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J24" s="10" t="b">
         <v>0</v>
@@ -2672,19 +2670,19 @@
     </row>
     <row r="25" ht="36.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C25" s="7">
         <v>250000.0</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D25&lt;&gt;"""", GOOGLETRANSLATE(D25, ""vi"", ""en""), """")
@@ -2701,7 +2699,7 @@
         <v>火锅汤底、辣椒酱、蔬菜和韩国面条。</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J25" s="10" t="b">
         <v>0</v>
@@ -2716,19 +2714,19 @@
     </row>
     <row r="26" ht="36.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" s="7">
         <v>55000.0</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F26" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D26&lt;&gt;"""", GOOGLETRANSLATE(D26, ""vi"", ""en""), """")
@@ -2745,7 +2743,7 @@
         <v>米饭、素咸鱼、素肉丝、素海带、葱（适量）</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J26" s="10" t="b">
         <v>0</v>
@@ -2760,19 +2758,19 @@
     </row>
     <row r="27" ht="36.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C27" s="7">
         <v>55000.0</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F27" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D27&lt;&gt;"""", GOOGLETRANSLATE(D27, ""vi"", ""en""), """")
@@ -2789,7 +2787,7 @@
         <v>米饭、菠萝、四季豆、胡萝卜、甜玉米、葱（根据口味调整）</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J27" s="10" t="b">
         <v>0</v>
@@ -2804,19 +2802,19 @@
     </row>
     <row r="28" ht="36.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C28" s="7">
         <v>55000.0</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F28" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D28&lt;&gt;"""", GOOGLETRANSLATE(D28, ""vi"", ""en""), """")
@@ -2833,7 +2831,7 @@
         <v>扬州炒饭：米饭、四季豆、胡萝卜、甜玉米、葱（可根据口味调整）</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J28" s="10" t="b">
         <v>0</v>
@@ -2848,19 +2846,19 @@
     </row>
     <row r="29" ht="36.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" s="12">
         <v>59000.0</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F29" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D29&lt;&gt;"""", GOOGLETRANSLATE(D29, ""vi"", ""en""), """")
@@ -2877,7 +2875,7 @@
         <v>米饭、豆芽、紫甘蓝、甜椒、甜玉米、芝麻花生、炸蘑菇，配韩式什锦饭酱。</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J29" s="10" t="b">
         <v>0</v>
@@ -2892,19 +2890,19 @@
     </row>
     <row r="30" ht="36.75" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C30" s="7">
         <v>55000.0</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F30" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D30&lt;&gt;"""", GOOGLETRANSLATE(D30, ""vi"", ""en""), """")
@@ -2921,7 +2919,7 @@
         <v>米饭、杏鲍菇、甜椒、洋葱、炸蒜，配蘸酱和蔬菜汤。</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J30" s="10" t="b">
         <v>0</v>
@@ -2936,19 +2934,19 @@
     </row>
     <row r="31" ht="36.75" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C31" s="7">
         <v>55000.0</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F31" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D31&lt;&gt;"""", GOOGLETRANSLATE(D31, ""vi"", ""en""), """")
@@ -2965,7 +2963,7 @@
         <v>米饭、杏鲍菇、红薯、胡萝卜、芋头、椰奶、咖喱香料，配蔬菜汤。</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J31" s="10" t="b">
         <v>0</v>
@@ -2980,19 +2978,19 @@
     </row>
     <row r="32" ht="36.75" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C32" s="7">
         <v>55000.0</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F32" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D32&lt;&gt;"""", GOOGLETRANSLATE(D32, ""vi"", ""en""), """")
@@ -3009,7 +3007,7 @@
         <v>韩国粉丝、小白菜、紫甘蓝、胡萝卜、炸平菇、粉丝酱。</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J32" s="10" t="b">
         <v>1</v>
@@ -3024,19 +3022,19 @@
     </row>
     <row r="33" ht="36.75" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C33" s="7">
         <v>55000.0</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F33" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D33&lt;&gt;"""", GOOGLETRANSLATE(D33, ""vi"", ""en""), """")
@@ -3053,7 +3051,7 @@
         <v>米粉、豆芽、韭菜、炸豆腐、炸蘑菇、罗望子酱，配烤花生、辣椒和青柠。</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J33" s="10" t="b">
         <v>1</v>
@@ -3068,19 +3066,19 @@
     </row>
     <row r="34" ht="36.75" customHeight="1">
       <c r="A34" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C34" s="7">
         <v>59000.0</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F34" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D34&lt;&gt;"""", GOOGLETRANSLATE(D34, ""vi"", ""en""), """")
@@ -3097,7 +3095,7 @@
         <v>米粉、甜椒、大白菜、洋葱、小白菜、炸豆腐、炸蘑菇、炸蒜。</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J34" s="10" t="b">
         <v>0</v>
@@ -3112,19 +3110,19 @@
     </row>
     <row r="35" ht="36.75" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C35" s="7">
         <v>59000.0</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F35" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D35&lt;&gt;"""", GOOGLETRANSLATE(D35, ""vi"", ""en""), """")
@@ -3141,7 +3139,7 @@
         <v>黄面条、甜椒、大白菜、洋葱、小白菜、炸豆腐、炸蘑菇、炸红葱头。</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J35" s="10" t="b">
         <v>0</v>
@@ -3156,19 +3154,19 @@
     </row>
     <row r="36" ht="36.75" customHeight="1">
       <c r="A36" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C36" s="7">
         <v>59000.0</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F36" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D36&lt;&gt;"""", GOOGLETRANSLATE(D36, ""vi"", ""en""), """")
@@ -3185,7 +3183,7 @@
         <v>意大利面、杏鲍菇、番茄酱。</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J36" s="10" t="b">
         <v>0</v>
@@ -3200,19 +3198,19 @@
     </row>
     <row r="37" ht="36.75" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" s="7">
         <v>65000.0</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F37" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D37&lt;&gt;"""", GOOGLETRANSLATE(D37, ""vi"", ""en""), """")
@@ -3229,7 +3227,7 @@
         <v>咖喱，面包</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J37" s="10" t="b">
         <v>0</v>
@@ -3244,19 +3242,19 @@
     </row>
     <row r="38" ht="36.75" customHeight="1">
       <c r="A38" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C38" s="7">
         <v>65000.0</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F38" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D38&lt;&gt;"""", GOOGLETRANSLATE(D38, ""vi"", ""en""), """")
@@ -3273,7 +3271,7 @@
         <v>蘑菇、土豆</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J38" s="10" t="b">
         <v>0</v>
@@ -3288,19 +3286,19 @@
     </row>
     <row r="39" ht="36.75" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C39" s="7">
         <v>50000.0</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F39" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D39&lt;&gt;"""", GOOGLETRANSLATE(D39, ""vi"", ""en""), """")
@@ -3316,8 +3314,8 @@
 "),"海带、豆腐、平菇、胡萝卜、炸洋葱、辣椒、生姜")</f>
         <v>海带、豆腐、平菇、胡萝卜、炸洋葱、辣椒、生姜</v>
       </c>
-      <c r="I39" s="16" t="s">
-        <v>157</v>
+      <c r="I39" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="J39" s="10" t="b">
         <v>0</v>
@@ -3332,19 +3330,19 @@
     </row>
     <row r="40" ht="36.75" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C40" s="7">
         <v>50000.0</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F40" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D40&lt;&gt;"""", GOOGLETRANSLATE(D40, ""vi"", ""en""), """")
@@ -3361,7 +3359,7 @@
         <v>薄荷、秋葵、豆芽、西红柿、菠萝、各种香草、炸蒜。</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J40" s="10" t="b">
         <v>0</v>
@@ -3376,19 +3374,19 @@
     </row>
     <row r="41" ht="36.75" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C41" s="7">
         <v>50000.0</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F41" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D41&lt;&gt;"""", GOOGLETRANSLATE(D41, ""vi"", ""en""), """")
@@ -3405,7 +3403,7 @@
         <v>大白菜、平菇、生姜、胡椒</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J41" s="10" t="b">
         <v>0</v>
@@ -3420,19 +3418,19 @@
     </row>
     <row r="42" ht="36.75" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C42" s="7">
         <v>39000.0</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F42" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D42&lt;&gt;"""", GOOGLETRANSLATE(D42, ""vi"", ""en""), """")
@@ -3440,8 +3438,8 @@
         <v>Sweet potato, sweet corn, carrots, mushrooms, green beans, fried onions, pepper, coriander</v>
       </c>
       <c r="G42" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E42,""en"",""zh"")"),"肥菜汤")</f>
-        <v>肥菜汤</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E42,""en"",""zh"")"),"发菜汤")</f>
+        <v>发菜汤</v>
       </c>
       <c r="H42" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D42&lt;&gt;"""", GOOGLETRANSLATE(F42, ""en"", ""zh""), """")
@@ -3449,7 +3447,7 @@
         <v>红薯、甜玉米、胡萝卜、蘑菇、四季豆、炸洋葱、辣椒、香菜</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J42" s="10" t="b">
         <v>0</v>
@@ -3464,19 +3462,19 @@
     </row>
     <row r="43" ht="36.75" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C43" s="7">
         <v>39000.0</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F43" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D43&lt;&gt;"""", GOOGLETRANSLATE(D43, ""vi"", ""en""), """")
@@ -3493,7 +3491,7 @@
         <v>银耳、莲子、胡萝卜菇、四季豆、炸洋葱、辣椒、香菜。</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J43" s="10" t="b">
         <v>0</v>
@@ -3508,19 +3506,19 @@
     </row>
     <row r="44" ht="36.75" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C44" s="7">
         <v>45000.0</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F44" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D44&lt;&gt;"""", GOOGLETRANSLATE(D44, ""vi"", ""en""), """")
@@ -3537,7 +3535,7 @@
         <v>空心菜和炸蒜，佐以酱油。</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J44" s="10" t="b">
         <v>0</v>
@@ -3552,19 +3550,19 @@
     </row>
     <row r="45" ht="36.75" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C45" s="7">
         <v>55000.0</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F45" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D45&lt;&gt;"""", GOOGLETRANSLATE(D45, ""vi"", ""en""), """")
@@ -3581,7 +3579,7 @@
         <v>空心菜、平菇和炸蒜，佐以酱油。</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J45" s="10" t="b">
         <v>0</v>
@@ -3596,19 +3594,19 @@
     </row>
     <row r="46" ht="36.75" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C46" s="7">
         <v>55000.0</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F46" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D46&lt;&gt;"""", GOOGLETRANSLATE(D46, ""vi"", ""en""), """")
@@ -3625,7 +3623,7 @@
         <v>大白菜、胡萝卜、甜椒、小白菜和炸蒜配酱油食用。</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J46" s="10" t="b">
         <v>0</v>
@@ -3640,19 +3638,19 @@
     </row>
     <row r="47" ht="36.75" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C47" s="7">
         <v>55000.0</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F47" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D47&lt;&gt;"""", GOOGLETRANSLATE(D47, ""vi"", ""en""), """")
@@ -3669,7 +3667,7 @@
         <v>大白菜、苦瓜、胡萝卜、小白菜、秋葵和葫芦可作为鱼露红烧肉的配菜。</v>
       </c>
       <c r="I47" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J47" s="10" t="b">
         <v>0</v>
@@ -3684,19 +3682,19 @@
     </row>
     <row r="48" ht="36.75" customHeight="1">
       <c r="A48" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C48" s="7">
         <v>55000.0</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F48" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D48&lt;&gt;"""", GOOGLETRANSLATE(D48, ""vi"", ""en""), """")
@@ -3713,7 +3711,7 @@
         <v>小白菜、胡萝卜、香菇、素蚝油</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J48" s="10" t="b">
         <v>0</v>
@@ -3728,19 +3726,19 @@
     </row>
     <row r="49" ht="36.75" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C49" s="7">
         <v>65000.0</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F49" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D49&lt;&gt;"""", GOOGLETRANSLATE(D49, ""vi"", ""en""), """")
@@ -3757,7 +3755,7 @@
         <v>杏鲍菇和黑胡椒酱</v>
       </c>
       <c r="I49" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J49" s="10" t="b">
         <v>0</v>
@@ -3772,19 +3770,19 @@
     </row>
     <row r="50" ht="36.75" customHeight="1">
       <c r="A50" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C50" s="7">
         <v>55000.0</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F50" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D50&lt;&gt;"""", GOOGLETRANSLATE(D50, ""vi"", ""en""), """")
@@ -3801,7 +3799,7 @@
         <v>胡萝卜、洋葱、蘑菇、四川酱</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J50" s="10" t="b">
         <v>0</v>
@@ -3816,19 +3814,19 @@
     </row>
     <row r="51" ht="36.75" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C51" s="7">
         <v>55000.0</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F51" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D51&lt;&gt;"""", GOOGLETRANSLATE(D51, ""vi"", ""en""), """")
@@ -3845,7 +3843,7 @@
         <v>泡菜火锅汤底，配紫甘蓝、大白菜、平菇和韩式面条。</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J51" s="10" t="b">
         <v>0</v>
@@ -3860,19 +3858,19 @@
     </row>
     <row r="52" ht="36.75" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C52" s="7">
         <v>55000.0</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F52" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D52&lt;&gt;"""", GOOGLETRANSLATE(D52, ""vi"", ""en""), """")
@@ -3889,7 +3887,7 @@
         <v>炸豆腐、洋葱、甜椒、沙爹酱</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J52" s="10" t="b">
         <v>0</v>
@@ -3904,19 +3902,19 @@
     </row>
     <row r="53" ht="36.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C53" s="7">
         <v>65000.0</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F53" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D53&lt;&gt;"""", GOOGLETRANSLATE(D53, ""vi"", ""en""), """")
@@ -3933,7 +3931,7 @@
         <v>草菇、洋葱、辣椒</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J53" s="10" t="b">
         <v>0</v>
@@ -3948,19 +3946,19 @@
     </row>
     <row r="54" ht="36.75" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C54" s="7">
         <v>65000.0</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F54" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D54&lt;&gt;"""", GOOGLETRANSLATE(D54, ""vi"", ""en""), """")
@@ -3977,7 +3975,7 @@
         <v>草菇、洋葱、辣椒</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="J54" s="10" t="b">
         <v>0</v>
@@ -3992,19 +3990,19 @@
     </row>
     <row r="55" ht="36.75" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C55" s="7">
         <v>35000.0</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F55" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D55&lt;&gt;"""", GOOGLETRANSLATE(D55, ""vi"", ""en""), """")
@@ -4021,7 +4019,7 @@
         <v>雪花莲、雪莲子、桃树脂、枸杞、红枣、龙眼</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J55" s="10" t="b">
         <v>0</v>
@@ -4036,19 +4034,19 @@
     </row>
     <row r="56" ht="36.75" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C56" s="7">
         <v>35000.0</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F56" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D56&lt;&gt;"""", GOOGLETRANSLATE(D56, ""vi"", ""en""), """")
@@ -4064,8 +4062,8 @@
 "),"莲子、枸杞、红枣、虫草")</f>
         <v>莲子、枸杞、红枣、虫草</v>
       </c>
-      <c r="I56" s="16" t="s">
-        <v>224</v>
+      <c r="I56" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="J56" s="10" t="b">
         <v>0</v>
@@ -4080,19 +4078,19 @@
     </row>
     <row r="57" ht="36.75" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C57" s="7">
         <v>35000.0</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F57" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D57&lt;&gt;"""", GOOGLETRANSLATE(D57, ""vi"", ""en""), """")
@@ -4109,7 +4107,7 @@
         <v>酸奶、桑葚酱、金橘酱、刨冰</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J57" s="10" t="b">
         <v>0</v>
@@ -4124,16 +4122,16 @@
     </row>
     <row r="58" ht="36.75" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C58" s="7">
         <v>12000.0</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E58" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B58,""vi"",""en"")"),"Panna Cotta (Blueberry, passion fruit, guava, peach, mulberry)")</f>
@@ -4154,7 +4152,7 @@
         <v>由纯豆浆和明胶制成，佐以各种果酱。</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J58" s="10" t="b">
         <v>0</v>
@@ -4245,11 +4243,13 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="22.75"/>
-    <col customWidth="1" min="4" max="4" width="56.13"/>
-    <col customWidth="1" min="5" max="5" width="30.25"/>
-    <col customWidth="1" min="6" max="6" width="26.0"/>
-    <col customWidth="1" min="8" max="8" width="17.25"/>
-    <col customWidth="1" min="9" max="9" width="31.38"/>
+    <col hidden="1" min="3" max="3" width="12.63"/>
+    <col customWidth="1" hidden="1" min="4" max="4" width="56.13"/>
+    <col customWidth="1" hidden="1" min="5" max="5" width="30.25"/>
+    <col customWidth="1" hidden="1" min="6" max="6" width="26.0"/>
+    <col hidden="1" min="7" max="7" width="12.63"/>
+    <col customWidth="1" hidden="1" min="8" max="8" width="17.25"/>
+    <col customWidth="1" min="9" max="9" width="82.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4284,27 +4284,27 @@
         <v>9</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C2" s="23">
         <v>35000.0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G2" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E2,""en"",""zh"")"),"花草茶")</f>
@@ -4316,7 +4316,7 @@
         <v>雏菊、玫瑰、枸杞、苹果、糖、冬虫夏草（可热食或冷食）</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J2" s="28" t="b">
         <v>0</v>
@@ -4326,24 +4326,24 @@
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="24.0" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C3" s="23">
         <v>35000.0</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G3" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E3,""en"",""zh"")"),"橙香柠檬草桃子茶")</f>
@@ -4355,7 +4355,7 @@
         <v>柠檬草碎、桃子茶、桃子糖浆、桃子果酱、金橘汁、桃片</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J3" s="28" t="b">
         <v>1</v>
@@ -4365,24 +4365,24 @@
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="24.0" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C4" s="23">
         <v>35000.0</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G4" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E4,""en"",""zh"")"),"荔枝茉莉花茶")</f>
@@ -4394,7 +4394,7 @@
         <v>荔枝糖浆，新鲜荔枝</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J4" s="28" t="b">
         <v>0</v>
@@ -4404,24 +4404,24 @@
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C5" s="23">
         <v>35000.0</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G5" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E5,""en"",""zh"")"),"粉红番石榴茶")</f>
@@ -4433,7 +4433,7 @@
         <v>金橘汁、番石榴果酱、番石榴糖浆、新鲜番石榴</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J5" s="28" t="b">
         <v>0</v>
@@ -4443,24 +4443,24 @@
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C6" s="23">
         <v>35000.0</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G6" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E6,""en"",""zh"")"),"蜂蜜姜热茶")</f>
@@ -4472,7 +4472,7 @@
         <v>姜茶、蜂蜜、姜片</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J6" s="28" t="b">
         <v>0</v>
@@ -4482,24 +4482,24 @@
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="24.0" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C7" s="23">
         <v>35000.0</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G7" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E7,""en"",""zh"")"),"烟熏金桔茶")</f>
@@ -4511,7 +4511,7 @@
         <v>烟灰、立顿茶、金橘汁、金橘果酱</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J7" s="28" t="b">
         <v>0</v>
@@ -4521,24 +4521,24 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="24.0" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C8" s="23">
         <v>35000.0</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G8" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E8,""en"",""zh"")"),"茉莉花茶")</f>
@@ -4550,7 +4550,7 @@
         <v>加入菠萝汁和棕榈果</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J8" s="28" t="b">
         <v>1</v>
@@ -4560,24 +4560,24 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C9" s="23">
         <v>35000.0</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G9" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E9,""en"",""zh"")"),"菠萝")</f>
@@ -4589,7 +4589,7 @@
         <v>菠萝汁</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J9" s="28" t="b">
         <v>0</v>
@@ -4599,24 +4599,24 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C10" s="23">
         <v>35000.0</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G10" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E10,""en"",""zh"")"),"橙子")</f>
@@ -4628,7 +4628,7 @@
         <v>橙汁</v>
       </c>
       <c r="I10" s="27" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J10" s="28" t="b">
         <v>0</v>
@@ -4638,24 +4638,24 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C11" s="23">
         <v>35000.0</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G11" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E11,""en"",""zh"")"),"西瓜")</f>
@@ -4667,7 +4667,7 @@
         <v>西瓜汁</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J11" s="28" t="b">
         <v>0</v>
@@ -4677,24 +4677,24 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="15.0" customHeight="1">
+    <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C12" s="23">
         <v>35000.0</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G12" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E12,""en"",""zh"")"),"百香果")</f>
@@ -4706,7 +4706,7 @@
         <v>百香果汁、百香果糖浆、百香果果酱</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J12" s="28" t="b">
         <v>0</v>
@@ -4716,24 +4716,24 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C13" s="23">
         <v>35000.0</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G13" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E13,""en"",""zh"")"),"橙胡萝卜")</f>
@@ -4744,8 +4744,8 @@
 "),"橙汁")</f>
         <v>橙汁</v>
       </c>
-      <c r="I13" s="30" t="s">
-        <v>293</v>
+      <c r="I13" s="27" t="s">
+        <v>295</v>
       </c>
       <c r="J13" s="28" t="b">
         <v>0</v>
@@ -4755,24 +4755,24 @@
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="C14" s="33">
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="32">
         <v>35000.0</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>295</v>
+      <c r="D14" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G14" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E14,""en"",""zh"")"),"菠萝胡萝卜")</f>
@@ -4783,35 +4783,35 @@
 "),"混合菠萝汁和胡萝卜汁")</f>
         <v>混合菠萝汁和胡萝卜汁</v>
       </c>
-      <c r="I14" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="J14" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="37" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
+      <c r="I14" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="J14" s="35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C15" s="23">
         <v>30000.0</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G15" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E15,""en"",""zh"")"),"蓝色海洋")</f>
@@ -4823,7 +4823,7 @@
         <v>蓝海精华液、薄荷精华液、柠檬汁、1-2片碾碎的薄荷叶、苏打水</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J15" s="28" t="b">
         <v>0</v>
@@ -4833,24 +4833,24 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C16" s="23">
         <v>30000.0</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G16" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E16,""en"",""zh"")"),"热带百香果")</f>
@@ -4862,7 +4862,7 @@
         <v>百香果精华液、百香果糖浆、苏打水</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J16" s="28" t="b">
         <v>0</v>
@@ -4872,24 +4872,24 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C17" s="23">
         <v>30000.0</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G17" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E17,""en"",""zh"")"),"清新酸爽")</f>
@@ -4901,7 +4901,7 @@
         <v>鲜榨柠檬汁、糖浆、苏打水</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J17" s="28" t="b">
         <v>0</v>
@@ -4911,24 +4911,24 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C18" s="23">
         <v>30000.0</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G18" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E18,""en"",""zh"")"),"紫色梦境")</f>
@@ -4936,11 +4936,11 @@
       </c>
       <c r="H18" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(F18&lt;&gt;"""", GOOGLETRANSLATE(F18, ""en"", ""zh""), """")
-"),"蓝莓汁、糖精、苏打水")</f>
-        <v>蓝莓汁、糖精、苏打水</v>
+"),"蓝莓汁、糖浆、苏打水")</f>
+        <v>蓝莓汁、糖浆、苏打水</v>
       </c>
       <c r="I18" s="27" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J18" s="28" t="b">
         <v>0</v>
@@ -4950,19 +4950,19 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C19" s="23">
         <v>35000.0</v>
       </c>
-      <c r="D19" s="38"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="25" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F19" s="25"/>
       <c r="G19" s="25" t="str">
@@ -4975,7 +4975,7 @@
         <v/>
       </c>
       <c r="I19" s="27" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J19" s="28" t="b">
         <v>0</v>
@@ -4985,19 +4985,19 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C20" s="23">
         <v>35000.0</v>
       </c>
-      <c r="D20" s="38"/>
+      <c r="D20" s="37"/>
       <c r="E20" s="25" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F20" s="25"/>
       <c r="G20" s="25" t="str">
@@ -5010,7 +5010,7 @@
         <v/>
       </c>
       <c r="I20" s="27" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J20" s="28" t="b">
         <v>0</v>
@@ -5020,24 +5020,24 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C21" s="23">
         <v>20000.0</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G21" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E21,""en"",""zh"")"),"冰黑咖啡 | 热黑咖啡")</f>
@@ -5048,7 +5048,7 @@
 "),"纯咖啡，加少许砂糖")</f>
         <v>纯咖啡，加少许砂糖</v>
       </c>
-      <c r="I21" s="38"/>
+      <c r="I21" s="37"/>
       <c r="J21" s="28" t="b">
         <v>1</v>
       </c>
@@ -5057,24 +5057,24 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C22" s="23">
         <v>25000.0</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G22" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E22,""en"",""zh"")"),"冰炼乳咖啡 | 热炼乳咖啡")</f>
@@ -5085,7 +5085,7 @@
 "),"纯咖啡，炼乳")</f>
         <v>纯咖啡，炼乳</v>
       </c>
-      <c r="I22" s="38"/>
+      <c r="I22" s="37"/>
       <c r="J22" s="28" t="b">
         <v>0</v>
       </c>
@@ -5094,24 +5094,24 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C23" s="23">
         <v>35000.0</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G23" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E23,""en"",""zh"")"),"白咖啡")</f>
@@ -5122,7 +5122,7 @@
 "),"纯咖啡、鲜牛奶、炼乳")</f>
         <v>纯咖啡、鲜牛奶、炼乳</v>
       </c>
-      <c r="I23" s="38"/>
+      <c r="I23" s="37"/>
       <c r="J23" s="28" t="b">
         <v>0</v>
       </c>
@@ -5131,24 +5131,24 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C24" s="23">
         <v>35000.0</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G24" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E24,""en"",""zh"")"),"咸奶油咖啡")</f>
@@ -5159,7 +5159,7 @@
 "),"纯咖啡、炼乳、咸奶油")</f>
         <v>纯咖啡、炼乳、咸奶油</v>
       </c>
-      <c r="I24" s="38"/>
+      <c r="I24" s="37"/>
       <c r="J24" s="28" t="b">
         <v>0</v>
       </c>
@@ -5168,19 +5168,19 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C25" s="23">
         <v>18000.0</v>
       </c>
-      <c r="D25" s="38"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="25" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F25" s="25"/>
       <c r="G25" s="25" t="str">
@@ -5192,7 +5192,7 @@
 "),"")</f>
         <v/>
       </c>
-      <c r="I25" s="38"/>
+      <c r="I25" s="37"/>
       <c r="J25" s="28" t="b">
         <v>0</v>
       </c>
@@ -5201,19 +5201,19 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C26" s="23">
         <v>18000.0</v>
       </c>
-      <c r="D26" s="38"/>
+      <c r="D26" s="37"/>
       <c r="E26" s="25" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F26" s="25"/>
       <c r="G26" s="25" t="str">
@@ -5225,7 +5225,7 @@
 "),"")</f>
         <v/>
       </c>
-      <c r="I26" s="38"/>
+      <c r="I26" s="37"/>
       <c r="J26" s="28" t="b">
         <v>0</v>
       </c>
@@ -5234,19 +5234,19 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>349</v>
-      </c>
-      <c r="C27" s="40">
+        <v>346</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C27" s="39">
         <v>18000.0</v>
       </c>
-      <c r="D27" s="38"/>
+      <c r="D27" s="37"/>
       <c r="E27" s="25" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F27" s="25"/>
       <c r="G27" s="25" t="str">
@@ -5258,7 +5258,7 @@
 "),"")</f>
         <v/>
       </c>
-      <c r="I27" s="38"/>
+      <c r="I27" s="37"/>
       <c r="J27" s="28" t="b">
         <v>0</v>
       </c>
@@ -5267,19 +5267,19 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>350</v>
+        <v>346</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>352</v>
       </c>
       <c r="C28" s="23">
         <v>18000.0</v>
       </c>
-      <c r="D28" s="38"/>
+      <c r="D28" s="37"/>
       <c r="E28" s="25" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F28" s="25"/>
       <c r="G28" s="25" t="str">
@@ -5291,7 +5291,7 @@
 "),"")</f>
         <v/>
       </c>
-      <c r="I28" s="38"/>
+      <c r="I28" s="37"/>
       <c r="J28" s="28" t="b">
         <v>0</v>
       </c>
@@ -5300,19 +5300,19 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="21" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C29" s="23">
         <v>12000.0</v>
       </c>
-      <c r="D29" s="38"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="25" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F29" s="25"/>
       <c r="G29" s="25" t="str">
@@ -5324,7 +5324,7 @@
 "),"")</f>
         <v/>
       </c>
-      <c r="I29" s="38"/>
+      <c r="I29" s="37"/>
       <c r="J29" s="28" t="b">
         <v>0</v>
       </c>
@@ -5372,139 +5372,139 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="B1" s="42" t="s">
+      <c r="A1" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" s="42" t="s">
+      <c r="A2" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="41" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>356</v>
+      <c r="A3" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>59</v>
+      <c r="A4" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>109</v>
+      <c r="A5" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>84</v>
+      <c r="A6" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="41" t="s">
         <v>357</v>
       </c>
+      <c r="B7" s="41" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>153</v>
+      <c r="A8" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>174</v>
+      <c r="A9" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="41" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="s">
-        <v>355</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>216</v>
+      <c r="A11" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>233</v>
+      <c r="A12" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="B13" s="42" t="s">
-        <v>269</v>
+      <c r="A13" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="B14" s="42" t="s">
-        <v>327</v>
+      <c r="A14" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="B15" s="42" t="s">
-        <v>320</v>
+      <c r="A15" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="B16" s="42" t="s">
-        <v>344</v>
+      <c r="A16" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="s">
-        <v>358</v>
-      </c>
-      <c r="B17" s="42" t="s">
-        <v>299</v>
+      <c r="A17" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -5525,94 +5525,94 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="s">
-        <v>359</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>360</v>
+      <c r="A1" s="41" t="s">
+        <v>361</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="str">
+      <c r="A2" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("FILTER(Category!B2:B1001, Category!A2:A1001=""food"")
 "),"special")</f>
         <v>special</v>
       </c>
-      <c r="B2" s="43" t="str">
+      <c r="B2" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("FILTER(Category!B3:B1001, Category!A3:A1001=""drink"")"),"tea")</f>
         <v>tea</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="str">
+      <c r="A3" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"appetizer")</f>
         <v>appetizer</v>
       </c>
-      <c r="B3" s="43" t="str">
+      <c r="B3" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"juice")</f>
         <v>juice</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="str">
+      <c r="A4" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"roll")</f>
         <v>roll</v>
       </c>
-      <c r="B4" s="43" t="str">
+      <c r="B4" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"coffee")</f>
         <v>coffee</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="str">
+      <c r="A5" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mainDish")</f>
         <v>mainDish</v>
       </c>
-      <c r="B5" s="43" t="str">
+      <c r="B5" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"thaiTea")</f>
         <v>thaiTea</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="str">
+      <c r="A6" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"hotPot")</f>
         <v>hotPot</v>
       </c>
-      <c r="B6" s="43" t="str">
+      <c r="B6" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"softdrink")</f>
         <v>softdrink</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="str">
+      <c r="A7" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ricePortion")</f>
         <v>ricePortion</v>
       </c>
-      <c r="B7" s="43" t="str">
+      <c r="B7" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"soda")</f>
         <v>soda</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="str">
+      <c r="A8" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"soup")</f>
         <v>soup</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="str">
+      <c r="A9" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"saltDish")</f>
         <v>saltDish</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="str">
+      <c r="A10" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"salad")</f>
         <v>salad</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="str">
+      <c r="A11" s="42" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"dessert")</f>
         <v>dessert</v>
       </c>

--- a/public/data/menu.xlsx
+++ b/public/data/menu.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="365">
   <si>
     <t>Category</t>
   </si>
@@ -123,7 +123,7 @@
     <t>spongy spongy potato</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151897/IMG_3736_ayg9jn.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328756/Khoai_t%C3%A2y_b%E1%BB%8Dt_bi%E1%BB%83n_khaivi_ifuygr.png</t>
   </si>
   <si>
     <t>salad</t>
@@ -171,7 +171,7 @@
     <t>Cartilage Algae Salad</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20rong%20su%CC%A3n_khaivi.jpg?alt=media&amp;token=5b7e2fcb-8602-40ec-85c0-22c4942a48ef</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780327653/G%E1%BB%8Fi_rong_s%E1%BB%A5n_khaivi_chx4ao.png</t>
   </si>
   <si>
     <t>SALAD Trái cây NHIỆT ĐỚi</t>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">Tropical Fruity Salad </t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1775977936/salad-rau_vyjipw.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326952/Salad_tr%C3%A1i_c%C3%A2y_nhi%E1%BB%87t_%C4%91%E1%BB%9Bi_khaivi3461_1_mojlce.png</t>
   </si>
   <si>
     <t>SALAD rong biển nhật</t>
@@ -222,7 +222,7 @@
     <t>Summer Roll</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncuon%2FGo%CC%89i%20cuo%CC%82%CC%81n_moncuon.jpg?alt=media&amp;token=07605767-b35d-4d6e-99b0-62f8fb4edd53</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780327622/G%E1%BB%8Fi_cu%E1%BB%91n_moncuon_ydfmll.png</t>
   </si>
   <si>
     <t>bì cuốn</t>
@@ -234,7 +234,7 @@
     <t>Crystal Autumn Roll</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncuon%2FBi%CC%80%20cuo%CC%82%CC%81n_moncuon.jpg?alt=media&amp;token=eb987c96-df54-461d-a485-5125061ea01f</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780327610/B%C3%AC_cu%E1%BB%91n_moncuon_yuwtur.png</t>
   </si>
   <si>
     <t>mẹt cuốn</t>
@@ -246,7 +246,7 @@
     <t>Veggie Wrap &amp; Roll</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncuon%2FMe%CC%A3t%20cuo%CC%82%CC%81n_moncuon.jpg?alt=media&amp;token=5f2bbf4c-bc70-4803-b68e-776a513ffdd6</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328753/M%E1%BA%B9t_cu%E1%BB%91n_moncuon_nzlfyn.png</t>
   </si>
   <si>
     <t>bánh xèo</t>
@@ -285,7 +285,7 @@
     <t>Green pepper &amp; mushrooms hotpot</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monlau%2FLa%CC%82%CC%89u%20na%CC%82%CC%81m%20ha%CC%82%CC%80m%20tie%CC%82u%20xanh_monlau.jpg?alt=media&amp;token=4bf45d0a-6d41-487c-99d6-e7b151289319</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326955/L%E1%BA%A9u_n%E1%BA%A5m_h%E1%BA%A7m_ti%C3%AAu_xanh_monlau3559_c74y1s.png</t>
   </si>
   <si>
     <t>lẩu thái</t>
@@ -321,7 +321,7 @@
     <t>furmented bean curd hotpot</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monlau%2FLa%CC%82%CC%89u%20chao_monlau.jpg?alt=media&amp;token=7c754995-1978-4ef9-881c-339b0742a3b2</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780326957/L%E1%BA%A9u_chao_monlau_fhdpv4.png</t>
   </si>
   <si>
     <t>lẩu kim chi hàn quốc</t>
@@ -384,6 +384,9 @@
     <t>Yang Chow fried rice</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328762/C%C6%A1m_chi%C3%AAn_d%C6%B0%C6%A1ng_ch%C3%A2u_monchinh3483_b6mfks.png</t>
+  </si>
+  <si>
     <t>cơm trộn hàn quốc</t>
   </si>
   <si>
@@ -435,6 +438,9 @@
     <t>hủ tiếu, giá đỗ, hẹ, đậu hũ chiên, nấm chiên, xốt me, dùng kèm lạc rang, ớt, chanh.</t>
   </si>
   <si>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328762/Pad_Th%C3%A1i_m%C3%B3n_n%E1%BB%95i_b%E1%BA%ADt_wmlydk.png</t>
+  </si>
+  <si>
     <t>HỦ TIẾU ÁP CHẢO</t>
   </si>
   <si>
@@ -504,7 +510,7 @@
     <t>Southern Vietnamese Sweet &amp; Sour Soup</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncanh%2FCanh%20chua%20Nam%20Bo%CC%A3%CC%82_moncanh.jpg?alt=media&amp;token=cb5f1c84-5c58-4665-8265-7a9d2270a86e</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328759/Canh_chua_Nam_B%E1%BB%99_moncanh_kj86vj.png</t>
   </si>
   <si>
     <t>CANH Cải xanh nấu nấm</t>
@@ -528,7 +534,7 @@
     <t>Fat Choy Soup</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncanh%2FSu%CC%81p%20to%CC%81c%20tie%CC%82n_moncanh.jpg?alt=media&amp;token=3078a31b-51f1-4ce8-a399-075cedf7e44b</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328745/S%C3%BAp_t%C3%B3c_ti%C3%AAn_moncanh-sup_ddgdgd.png</t>
   </si>
   <si>
     <t>SÚP NẤM TUYẾT HẠT SEN</t>
@@ -540,7 +546,7 @@
     <t>Lotus seed &amp; White Wood-ear Mushroom Soup</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncanh%2FSu%CC%81p%20na%CC%82%CC%81m%20tuye%CC%82%CC%81t%20he%CC%A3t%20sen_moncanh.jpg?alt=media&amp;token=c1843967-442e-44f4-aa0d-8a1d7a8f0c15</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328717/S%C3%BAp_n%E1%BA%A5m_tuy%E1%BA%BFt_h%E1%BA%B9t_sen_moncanh-sup_xawwyb.png</t>
   </si>
   <si>
     <t>saltDish</t>
@@ -579,7 +585,7 @@
     <t>Mixed Stir-fried Veggies</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151903/IMG_3860_rxyxxc.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328727/Rau_x%C3%A0o_th%E1%BA%ADp_c%E1%BA%A9m_monman__znkw6v.png</t>
   </si>
   <si>
     <t>RAU LUỘC KHO QUẸT</t>
@@ -591,7 +597,7 @@
     <t>Boiled Veggie with Caramelized Salted Sauce</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monman%2FRau%20luo%CC%A3%CC%82c-kho%20que%CC%A3t_monman.jpg?alt=media&amp;token=3886a8a4-402d-4df7-a8c4-4d96b2e8af02</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780328714/Rau_lu%E1%BB%99c-kho_qu%E1%BA%B9t_monman_ot8eog.png</t>
   </si>
   <si>
     <t>CẢI THÌA SỐT NẤM ĐÔNG CÔ</t>
@@ -2831,7 +2837,7 @@
         <v>扬州炒饭：米饭、四季豆、胡萝卜、甜玉米、葱（可根据口味调整）</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J28" s="10" t="b">
         <v>0</v>
@@ -2849,16 +2855,16 @@
         <v>110</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C29" s="12">
         <v>59000.0</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F29" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D29&lt;&gt;"""", GOOGLETRANSLATE(D29, ""vi"", ""en""), """")
@@ -2875,7 +2881,7 @@
         <v>米饭、豆芽、紫甘蓝、甜椒、甜玉米、芝麻花生、炸蘑菇，配韩式什锦饭酱。</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J29" s="10" t="b">
         <v>0</v>
@@ -2893,16 +2899,16 @@
         <v>110</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C30" s="7">
         <v>55000.0</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F30" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D30&lt;&gt;"""", GOOGLETRANSLATE(D30, ""vi"", ""en""), """")
@@ -2919,7 +2925,7 @@
         <v>米饭、杏鲍菇、甜椒、洋葱、炸蒜，配蘸酱和蔬菜汤。</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J30" s="10" t="b">
         <v>0</v>
@@ -2937,16 +2943,16 @@
         <v>110</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C31" s="7">
         <v>55000.0</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F31" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D31&lt;&gt;"""", GOOGLETRANSLATE(D31, ""vi"", ""en""), """")
@@ -2963,7 +2969,7 @@
         <v>米饭、杏鲍菇、红薯、胡萝卜、芋头、椰奶、咖喱香料，配蔬菜汤。</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J31" s="10" t="b">
         <v>0</v>
@@ -2981,13 +2987,13 @@
         <v>110</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C32" s="7">
         <v>55000.0</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>104</v>
@@ -3007,7 +3013,7 @@
         <v>韩国粉丝、小白菜、紫甘蓝、胡萝卜、炸平菇、粉丝酱。</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J32" s="10" t="b">
         <v>1</v>
@@ -3025,13 +3031,13 @@
         <v>110</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C33" s="7">
         <v>55000.0</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>104</v>
@@ -3051,7 +3057,7 @@
         <v>米粉、豆芽、韭菜、炸豆腐、炸蘑菇、罗望子酱，配烤花生、辣椒和青柠。</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="J33" s="10" t="b">
         <v>1</v>
@@ -3069,13 +3075,13 @@
         <v>110</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C34" s="7">
         <v>59000.0</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>104</v>
@@ -3095,7 +3101,7 @@
         <v>米粉、甜椒、大白菜、洋葱、小白菜、炸豆腐、炸蘑菇、炸蒜。</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J34" s="10" t="b">
         <v>0</v>
@@ -3113,13 +3119,13 @@
         <v>110</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C35" s="7">
         <v>59000.0</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>104</v>
@@ -3139,7 +3145,7 @@
         <v>黄面条、甜椒、大白菜、洋葱、小白菜、炸豆腐、炸蘑菇、炸红葱头。</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J35" s="10" t="b">
         <v>0</v>
@@ -3157,13 +3163,13 @@
         <v>110</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C36" s="7">
         <v>59000.0</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>104</v>
@@ -3183,7 +3189,7 @@
         <v>意大利面、杏鲍菇、番茄酱。</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J36" s="10" t="b">
         <v>0</v>
@@ -3201,13 +3207,13 @@
         <v>110</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C37" s="7">
         <v>65000.0</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>104</v>
@@ -3227,7 +3233,7 @@
         <v>咖喱，面包</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J37" s="10" t="b">
         <v>0</v>
@@ -3245,13 +3251,13 @@
         <v>110</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C38" s="7">
         <v>65000.0</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>104</v>
@@ -3271,7 +3277,7 @@
         <v>蘑菇、土豆</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J38" s="10" t="b">
         <v>0</v>
@@ -3286,19 +3292,19 @@
     </row>
     <row r="39" ht="36.75" customHeight="1">
       <c r="A39" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C39" s="7">
         <v>50000.0</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F39" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D39&lt;&gt;"""", GOOGLETRANSLATE(D39, ""vi"", ""en""), """")
@@ -3315,7 +3321,7 @@
         <v>海带、豆腐、平菇、胡萝卜、炸洋葱、辣椒、生姜</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J39" s="10" t="b">
         <v>0</v>
@@ -3330,19 +3336,19 @@
     </row>
     <row r="40" ht="36.75" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C40" s="7">
         <v>50000.0</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F40" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D40&lt;&gt;"""", GOOGLETRANSLATE(D40, ""vi"", ""en""), """")
@@ -3358,8 +3364,8 @@
 "),"薄荷、秋葵、豆芽、西红柿、菠萝、各种香草、炸蒜。")</f>
         <v>薄荷、秋葵、豆芽、西红柿、菠萝、各种香草、炸蒜。</v>
       </c>
-      <c r="I40" s="16" t="s">
-        <v>162</v>
+      <c r="I40" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="J40" s="10" t="b">
         <v>0</v>
@@ -3374,19 +3380,19 @@
     </row>
     <row r="41" ht="36.75" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C41" s="7">
         <v>50000.0</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F41" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D41&lt;&gt;"""", GOOGLETRANSLATE(D41, ""vi"", ""en""), """")
@@ -3403,7 +3409,7 @@
         <v>大白菜、平菇、生姜、胡椒</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J41" s="10" t="b">
         <v>0</v>
@@ -3418,19 +3424,19 @@
     </row>
     <row r="42" ht="36.75" customHeight="1">
       <c r="A42" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C42" s="7">
         <v>39000.0</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F42" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D42&lt;&gt;"""", GOOGLETRANSLATE(D42, ""vi"", ""en""), """")
@@ -3446,8 +3452,8 @@
 "),"红薯、甜玉米、胡萝卜、蘑菇、四季豆、炸洋葱、辣椒、香菜")</f>
         <v>红薯、甜玉米、胡萝卜、蘑菇、四季豆、炸洋葱、辣椒、香菜</v>
       </c>
-      <c r="I42" s="16" t="s">
-        <v>170</v>
+      <c r="I42" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="J42" s="10" t="b">
         <v>0</v>
@@ -3462,19 +3468,19 @@
     </row>
     <row r="43" ht="36.75" customHeight="1">
       <c r="A43" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C43" s="7">
         <v>39000.0</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F43" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D43&lt;&gt;"""", GOOGLETRANSLATE(D43, ""vi"", ""en""), """")
@@ -3490,8 +3496,8 @@
 "),"银耳、莲子、胡萝卜菇、四季豆、炸洋葱、辣椒、香菜。")</f>
         <v>银耳、莲子、胡萝卜菇、四季豆、炸洋葱、辣椒、香菜。</v>
       </c>
-      <c r="I43" s="16" t="s">
-        <v>174</v>
+      <c r="I43" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="J43" s="10" t="b">
         <v>0</v>
@@ -3506,19 +3512,19 @@
     </row>
     <row r="44" ht="36.75" customHeight="1">
       <c r="A44" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C44" s="7">
         <v>45000.0</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F44" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D44&lt;&gt;"""", GOOGLETRANSLATE(D44, ""vi"", ""en""), """")
@@ -3535,7 +3541,7 @@
         <v>空心菜和炸蒜，佐以酱油。</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J44" s="10" t="b">
         <v>0</v>
@@ -3550,19 +3556,19 @@
     </row>
     <row r="45" ht="36.75" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C45" s="7">
         <v>55000.0</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F45" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D45&lt;&gt;"""", GOOGLETRANSLATE(D45, ""vi"", ""en""), """")
@@ -3579,7 +3585,7 @@
         <v>空心菜、平菇和炸蒜，佐以酱油。</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J45" s="10" t="b">
         <v>0</v>
@@ -3594,19 +3600,19 @@
     </row>
     <row r="46" ht="36.75" customHeight="1">
       <c r="A46" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C46" s="7">
         <v>55000.0</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F46" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D46&lt;&gt;"""", GOOGLETRANSLATE(D46, ""vi"", ""en""), """")
@@ -3623,7 +3629,7 @@
         <v>大白菜、胡萝卜、甜椒、小白菜和炸蒜配酱油食用。</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J46" s="10" t="b">
         <v>0</v>
@@ -3638,19 +3644,19 @@
     </row>
     <row r="47" ht="36.75" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C47" s="7">
         <v>55000.0</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F47" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D47&lt;&gt;"""", GOOGLETRANSLATE(D47, ""vi"", ""en""), """")
@@ -3666,8 +3672,8 @@
 "),"大白菜、苦瓜、胡萝卜、小白菜、秋葵和葫芦可作为鱼露红烧肉的配菜。")</f>
         <v>大白菜、苦瓜、胡萝卜、小白菜、秋葵和葫芦可作为鱼露红烧肉的配菜。</v>
       </c>
-      <c r="I47" s="16" t="s">
-        <v>191</v>
+      <c r="I47" s="9" t="s">
+        <v>193</v>
       </c>
       <c r="J47" s="10" t="b">
         <v>0</v>
@@ -3682,19 +3688,19 @@
     </row>
     <row r="48" ht="36.75" customHeight="1">
       <c r="A48" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C48" s="7">
         <v>55000.0</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F48" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D48&lt;&gt;"""", GOOGLETRANSLATE(D48, ""vi"", ""en""), """")
@@ -3711,7 +3717,7 @@
         <v>小白菜、胡萝卜、香菇、素蚝油</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J48" s="10" t="b">
         <v>0</v>
@@ -3726,19 +3732,19 @@
     </row>
     <row r="49" ht="36.75" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C49" s="7">
         <v>65000.0</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F49" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D49&lt;&gt;"""", GOOGLETRANSLATE(D49, ""vi"", ""en""), """")
@@ -3755,7 +3761,7 @@
         <v>杏鲍菇和黑胡椒酱</v>
       </c>
       <c r="I49" s="16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J49" s="10" t="b">
         <v>0</v>
@@ -3770,19 +3776,19 @@
     </row>
     <row r="50" ht="36.75" customHeight="1">
       <c r="A50" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C50" s="7">
         <v>55000.0</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F50" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D50&lt;&gt;"""", GOOGLETRANSLATE(D50, ""vi"", ""en""), """")
@@ -3799,7 +3805,7 @@
         <v>胡萝卜、洋葱、蘑菇、四川酱</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J50" s="10" t="b">
         <v>0</v>
@@ -3814,10 +3820,10 @@
     </row>
     <row r="51" ht="36.75" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C51" s="7">
         <v>55000.0</v>
@@ -3826,7 +3832,7 @@
         <v>103</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F51" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D51&lt;&gt;"""", GOOGLETRANSLATE(D51, ""vi"", ""en""), """")
@@ -3843,7 +3849,7 @@
         <v>泡菜火锅汤底，配紫甘蓝、大白菜、平菇和韩式面条。</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J51" s="10" t="b">
         <v>0</v>
@@ -3858,19 +3864,19 @@
     </row>
     <row r="52" ht="36.75" customHeight="1">
       <c r="A52" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C52" s="7">
         <v>55000.0</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F52" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D52&lt;&gt;"""", GOOGLETRANSLATE(D52, ""vi"", ""en""), """")
@@ -3887,7 +3893,7 @@
         <v>炸豆腐、洋葱、甜椒、沙爹酱</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J52" s="10" t="b">
         <v>0</v>
@@ -3902,19 +3908,19 @@
     </row>
     <row r="53" ht="36.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C53" s="7">
         <v>65000.0</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F53" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D53&lt;&gt;"""", GOOGLETRANSLATE(D53, ""vi"", ""en""), """")
@@ -3931,7 +3937,7 @@
         <v>草菇、洋葱、辣椒</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J53" s="10" t="b">
         <v>0</v>
@@ -3946,19 +3952,19 @@
     </row>
     <row r="54" ht="36.75" customHeight="1">
       <c r="A54" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C54" s="7">
         <v>65000.0</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F54" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D54&lt;&gt;"""", GOOGLETRANSLATE(D54, ""vi"", ""en""), """")
@@ -3975,7 +3981,7 @@
         <v>草菇、洋葱、辣椒</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J54" s="10" t="b">
         <v>0</v>
@@ -3990,19 +3996,19 @@
     </row>
     <row r="55" ht="36.75" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C55" s="7">
         <v>35000.0</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F55" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D55&lt;&gt;"""", GOOGLETRANSLATE(D55, ""vi"", ""en""), """")
@@ -4019,7 +4025,7 @@
         <v>雪花莲、雪莲子、桃树脂、枸杞、红枣、龙眼</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J55" s="10" t="b">
         <v>0</v>
@@ -4034,19 +4040,19 @@
     </row>
     <row r="56" ht="36.75" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C56" s="7">
         <v>35000.0</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F56" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D56&lt;&gt;"""", GOOGLETRANSLATE(D56, ""vi"", ""en""), """")
@@ -4063,7 +4069,7 @@
         <v>莲子、枸杞、红枣、虫草</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J56" s="10" t="b">
         <v>0</v>
@@ -4078,19 +4084,19 @@
     </row>
     <row r="57" ht="36.75" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C57" s="7">
         <v>35000.0</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F57" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("IF(D57&lt;&gt;"""", GOOGLETRANSLATE(D57, ""vi"", ""en""), """")
@@ -4107,7 +4113,7 @@
         <v>酸奶、桑葚酱、金橘酱、刨冰</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J57" s="10" t="b">
         <v>0</v>
@@ -4122,16 +4128,16 @@
     </row>
     <row r="58" ht="36.75" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C58" s="7">
         <v>12000.0</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E58" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B58,""vi"",""en"")"),"Panna Cotta (Blueberry, passion fruit, guava, peach, mulberry)")</f>
@@ -4152,7 +4158,7 @@
         <v>由纯豆浆和明胶制成，佐以各种果酱。</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J58" s="10" t="b">
         <v>0</v>
@@ -4284,27 +4290,27 @@
         <v>9</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C2" s="23">
         <v>35000.0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G2" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E2,""en"",""zh"")"),"花草茶")</f>
@@ -4316,7 +4322,7 @@
         <v>雏菊、玫瑰、枸杞、苹果、糖、冬虫夏草（可热食或冷食）</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J2" s="28" t="b">
         <v>0</v>
@@ -4328,22 +4334,22 @@
     </row>
     <row r="3" ht="24.0" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C3" s="23">
         <v>35000.0</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G3" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E3,""en"",""zh"")"),"橙香柠檬草桃子茶")</f>
@@ -4355,7 +4361,7 @@
         <v>柠檬草碎、桃子茶、桃子糖浆、桃子果酱、金橘汁、桃片</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J3" s="28" t="b">
         <v>1</v>
@@ -4367,22 +4373,22 @@
     </row>
     <row r="4" ht="24.0" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C4" s="23">
         <v>35000.0</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G4" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E4,""en"",""zh"")"),"荔枝茉莉花茶")</f>
@@ -4394,7 +4400,7 @@
         <v>荔枝糖浆，新鲜荔枝</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J4" s="28" t="b">
         <v>0</v>
@@ -4406,22 +4412,22 @@
     </row>
     <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C5" s="23">
         <v>35000.0</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G5" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E5,""en"",""zh"")"),"粉红番石榴茶")</f>
@@ -4433,7 +4439,7 @@
         <v>金橘汁、番石榴果酱、番石榴糖浆、新鲜番石榴</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J5" s="28" t="b">
         <v>0</v>
@@ -4445,22 +4451,22 @@
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C6" s="23">
         <v>35000.0</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G6" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E6,""en"",""zh"")"),"蜂蜜姜热茶")</f>
@@ -4472,7 +4478,7 @@
         <v>姜茶、蜂蜜、姜片</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J6" s="28" t="b">
         <v>0</v>
@@ -4484,22 +4490,22 @@
     </row>
     <row r="7" ht="24.0" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C7" s="23">
         <v>35000.0</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G7" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E7,""en"",""zh"")"),"烟熏金桔茶")</f>
@@ -4511,7 +4517,7 @@
         <v>烟灰、立顿茶、金橘汁、金橘果酱</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J7" s="28" t="b">
         <v>0</v>
@@ -4523,22 +4529,22 @@
     </row>
     <row r="8" ht="24.0" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C8" s="23">
         <v>35000.0</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G8" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E8,""en"",""zh"")"),"茉莉花茶")</f>
@@ -4550,7 +4556,7 @@
         <v>加入菠萝汁和棕榈果</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J8" s="28" t="b">
         <v>1</v>
@@ -4562,22 +4568,22 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C9" s="23">
         <v>35000.0</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G9" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E9,""en"",""zh"")"),"菠萝")</f>
@@ -4589,7 +4595,7 @@
         <v>菠萝汁</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J9" s="28" t="b">
         <v>0</v>
@@ -4601,22 +4607,22 @@
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C10" s="23">
         <v>35000.0</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G10" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E10,""en"",""zh"")"),"橙子")</f>
@@ -4628,7 +4634,7 @@
         <v>橙汁</v>
       </c>
       <c r="I10" s="27" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J10" s="28" t="b">
         <v>0</v>
@@ -4640,22 +4646,22 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C11" s="23">
         <v>35000.0</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G11" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E11,""en"",""zh"")"),"西瓜")</f>
@@ -4667,7 +4673,7 @@
         <v>西瓜汁</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J11" s="28" t="b">
         <v>0</v>
@@ -4679,22 +4685,22 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C12" s="23">
         <v>35000.0</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G12" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E12,""en"",""zh"")"),"百香果")</f>
@@ -4706,7 +4712,7 @@
         <v>百香果汁、百香果糖浆、百香果果酱</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J12" s="28" t="b">
         <v>0</v>
@@ -4718,22 +4724,22 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C13" s="23">
         <v>35000.0</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G13" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E13,""en"",""zh"")"),"橙胡萝卜")</f>
@@ -4745,7 +4751,7 @@
         <v>橙汁</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J13" s="28" t="b">
         <v>0</v>
@@ -4757,22 +4763,22 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="30" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C14" s="32">
         <v>35000.0</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G14" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E14,""en"",""zh"")"),"菠萝胡萝卜")</f>
@@ -4784,7 +4790,7 @@
         <v>混合菠萝汁和胡萝卜汁</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J14" s="35" t="b">
         <v>0</v>
@@ -4796,22 +4802,22 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C15" s="23">
         <v>30000.0</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G15" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E15,""en"",""zh"")"),"蓝色海洋")</f>
@@ -4823,7 +4829,7 @@
         <v>蓝海精华液、薄荷精华液、柠檬汁、1-2片碾碎的薄荷叶、苏打水</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J15" s="28" t="b">
         <v>0</v>
@@ -4835,22 +4841,22 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C16" s="23">
         <v>30000.0</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G16" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E16,""en"",""zh"")"),"热带百香果")</f>
@@ -4862,7 +4868,7 @@
         <v>百香果精华液、百香果糖浆、苏打水</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J16" s="28" t="b">
         <v>0</v>
@@ -4874,22 +4880,22 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C17" s="23">
         <v>30000.0</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G17" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E17,""en"",""zh"")"),"清新酸爽")</f>
@@ -4901,7 +4907,7 @@
         <v>鲜榨柠檬汁、糖浆、苏打水</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J17" s="28" t="b">
         <v>0</v>
@@ -4913,22 +4919,22 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C18" s="23">
         <v>30000.0</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G18" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E18,""en"",""zh"")"),"紫色梦境")</f>
@@ -4940,7 +4946,7 @@
         <v>蓝莓汁、糖浆、苏打水</v>
       </c>
       <c r="I18" s="27" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J18" s="28" t="b">
         <v>0</v>
@@ -4952,17 +4958,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="21" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C19" s="23">
         <v>35000.0</v>
       </c>
       <c r="D19" s="37"/>
       <c r="E19" s="25" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F19" s="25"/>
       <c r="G19" s="25" t="str">
@@ -4975,7 +4981,7 @@
         <v/>
       </c>
       <c r="I19" s="27" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J19" s="28" t="b">
         <v>0</v>
@@ -4987,17 +4993,17 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C20" s="23">
         <v>35000.0</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="25" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F20" s="25"/>
       <c r="G20" s="25" t="str">
@@ -5010,7 +5016,7 @@
         <v/>
       </c>
       <c r="I20" s="27" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J20" s="28" t="b">
         <v>0</v>
@@ -5022,22 +5028,22 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C21" s="23">
         <v>20000.0</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G21" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E21,""en"",""zh"")"),"冰黑咖啡 | 热黑咖啡")</f>
@@ -5059,22 +5065,22 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C22" s="23">
         <v>25000.0</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G22" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E22,""en"",""zh"")"),"冰炼乳咖啡 | 热炼乳咖啡")</f>
@@ -5096,22 +5102,22 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C23" s="23">
         <v>35000.0</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G23" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E23,""en"",""zh"")"),"白咖啡")</f>
@@ -5133,22 +5139,22 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C24" s="23">
         <v>35000.0</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G24" s="25" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(E24,""en"",""zh"")"),"咸奶油咖啡")</f>
@@ -5170,17 +5176,17 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C25" s="23">
         <v>18000.0</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="25" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F25" s="25"/>
       <c r="G25" s="25" t="str">
@@ -5203,17 +5209,17 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C26" s="23">
         <v>18000.0</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="25" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F26" s="25"/>
       <c r="G26" s="25" t="str">
@@ -5236,17 +5242,17 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C27" s="39">
         <v>18000.0</v>
       </c>
       <c r="D27" s="37"/>
       <c r="E27" s="25" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F27" s="25"/>
       <c r="G27" s="25" t="str">
@@ -5269,17 +5275,17 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C28" s="23">
         <v>18000.0</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="25" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F28" s="25"/>
       <c r="G28" s="25" t="str">
@@ -5302,17 +5308,17 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C29" s="23">
         <v>12000.0</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="25" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F29" s="25"/>
       <c r="G29" s="25" t="str">
@@ -5373,7 +5379,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B1" s="41" t="s">
         <v>1</v>
@@ -5381,7 +5387,7 @@
     </row>
     <row r="2">
       <c r="A2" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>11</v>
@@ -5389,15 +5395,15 @@
     </row>
     <row r="3">
       <c r="A3" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>60</v>
@@ -5405,7 +5411,7 @@
     </row>
     <row r="5">
       <c r="A5" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B5" s="41" t="s">
         <v>110</v>
@@ -5413,7 +5419,7 @@
     </row>
     <row r="6">
       <c r="A6" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B6" s="41" t="s">
         <v>85</v>
@@ -5421,31 +5427,31 @@
     </row>
     <row r="7">
       <c r="A7" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B10" s="41" t="s">
         <v>36</v>
@@ -5453,58 +5459,58 @@
     </row>
     <row r="11">
       <c r="A11" s="41" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="41" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -5526,10 +5532,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="41" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">

--- a/public/data/menu.xlsx
+++ b/public/data/menu.xlsx
@@ -87,7 +87,7 @@
     <t>Fried Young Tofu with Meat floss</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151896/IMG_3758_mdxtav.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780330621/%C4%90%E1%BA%ADu_h%C5%A9_non_chi%C3%AAn_gi%C3%B2n_ch%C3%A0_b%C3%B4ng_dacbiet_2_1_vf9gj1.png</t>
   </si>
   <si>
     <t>NẤM bào ngư xốc muối hongkong</t>
@@ -99,7 +99,7 @@
     <t>HongKong Salted Oyster Mushrooms</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/dacbiet%2FNa%CC%82%CC%81m%20ba%CC%80o%20ngu%CC%9B%20xo%CC%82%CC%81c%20muo%CC%82%CC%81i%20HongKong_dacbiet.jpg?alt=media&amp;token=7158a1fe-cd82-4452-a322-31ac284da192</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780330085/N%E1%BA%A5m_b%C3%A0o_ng%C6%B0_x%E1%BB%91c_mu%E1%BB%91i_HongKong_dacbiet_2_ioqrqe.png</t>
   </si>
   <si>
     <t>ĐẬU NON RONG BIỂN SỐT TERIYAKI</t>
@@ -111,7 +111,7 @@
     <t>Seaweed rolled Young Tofu &amp; Teriyaki Sauce</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151906/IMG_3883_ip1sfc.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329928/IMG_3883_ngddl5.jpg</t>
   </si>
   <si>
     <t>KHOAI TÂY BỌT BIỂN</t>
@@ -135,7 +135,7 @@
     <t>nấm bào ngư, tàu hủ ki, rau thơm các loại, xốt gỏi chua cay</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FGo%CC%89i%20na%CC%82%CC%81m%20ba%CC%80o%20ngu%CC%9B%20xe%CC%81%20tro%CC%A3%CC%82n_%20khaivi.jpg?alt=media&amp;token=afb1b5fc-4db0-4562-88cd-75c1ddc67200</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329423/G%E1%BB%8Fi_n%E1%BA%A5m_b%C3%A0o_ng%C6%B0_x%C3%A9_tr%E1%BB%99n__khaivi3458_x9g1lk.png</t>
   </si>
   <si>
     <t>GỎI somtum thái lan</t>
@@ -159,7 +159,7 @@
     <t xml:space="preserve">Lotus Delight Salad </t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151915/IMG_4017_cp8wde.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780330013/IMG_4017_onffyz.jpg</t>
   </si>
   <si>
     <t>GỎI RONG SỤN</t>
@@ -195,7 +195,7 @@
     <t>Japanese Seaweed Salad</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/khaivi%2FSalad%20rong%20bie%CC%82%CC%89n%20Nha%CC%A3%CC%82t_khaivi.jpg?alt=media&amp;token=1228fe8a-ff61-4009-968d-e5a09d34ca98</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780330359/Salad_rong_bi%E1%BB%83n_Nh%E1%BA%ADt_khaivi3480_sobwrv.png</t>
   </si>
   <si>
     <t>roll</t>
@@ -270,7 +270,7 @@
     <t>Grilled mushrooms rolled in piper lolot</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/moncuon%2FNa%CC%82%CC%81m%20nu%CC%9Bo%CC%9B%CC%81ng%20la%CC%81%20lo%CC%82%CC%81t_moncuon.jpg?alt=media&amp;token=ca047dfa-9e00-4c09-8c95-7577d2a1cbcc</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329435/N%E1%BA%A5m_n%C6%B0%E1%BB%9Bng_l%C3%A1_l%E1%BB%91t_moncuon3505_wcaxnb.png</t>
   </si>
   <si>
     <t>hotPot</t>
@@ -360,7 +360,7 @@
     <t>fried rice with seaweed</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monchinh%2FCo%CC%9Bm%20chie%CC%82n%20rong%20bie%CC%82%CC%89n_monchinh.jpg?alt=media&amp;token=5df048ec-8ec7-4a03-912b-15bd37cde101</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780330923/C%C6%A1m_chi%C3%AAn_rong_bi%E1%BB%83n_monchinh_1_xg1xfe.png</t>
   </si>
   <si>
     <t>cơm chiên thơm kiểu thái</t>
@@ -372,7 +372,7 @@
     <t>Thai fried rice with pineapple</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151911/IMG_4007_sdommt.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329706/IMG_4007_b21u97.jpg</t>
   </si>
   <si>
     <t>cơm chiên dương châu</t>
@@ -396,7 +396,7 @@
     <t>korean mixed rice</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monchinh%2FCo%CC%9Bm%20tro%CC%A3%CC%82n%20Ha%CC%80n%20Quo%CC%82%CC%81c_monchinh.jpg?alt=media&amp;token=37e45fe4-94e0-48e9-a3c8-28a441007484</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780330955/C%C6%A1m_tr%E1%BB%99n_H%C3%A0n_Qu%E1%BB%91c_monchinh_2_y0zjwf.png</t>
   </si>
   <si>
     <t>cơm nấm lúc lắc &amp; canh rau củ</t>
@@ -429,7 +429,7 @@
     <t>miến Hàn Quốc, cải thìa, bắp cải tím, cà rốt, nấm bào ngư chiên, xốt miến trộn.</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monchinh%2FMie%CC%82%CC%81n%20tro%CC%A3%CC%82n_monchinh.jpg?alt=media&amp;token=393756ca-c3e1-4280-b271-92e3143fd814</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329431/Mi%E1%BA%BFn_tr%E1%BB%99n_monchinh_l9zxsg.png</t>
   </si>
   <si>
     <t>PAD thái</t>
@@ -456,7 +456,7 @@
     <t>Mì vàng, ớt chuông, cải thảo, hành tây, cải thài, đậu hũ chiên, nấm chiên, hành phi.</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monchinh%2FMi%CC%80%20va%CC%80ng%20xa%CC%80o%20tha%CC%A3%CC%82p%20ca%CC%82%CC%89m_monchinh.jpg?alt=media&amp;token=80fe2512-f39c-4a72-ade1-5c84dea2f3dc</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780330945/M%C3%AC_v%C3%A0ng_x%C3%A0o_th%E1%BA%ADp_c%E1%BA%A9m_monchinh_1_dzifz6.png</t>
   </si>
   <si>
     <t>MÌ Ý SỐT CÀ CHUA NẤM</t>
@@ -474,7 +474,7 @@
     <t>cà ri, bánh mì</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monchinh%2FCa%CC%80%20ri%20ba%CC%81nh%20mi%CC%80_monchinh.jpg?alt=media&amp;token=a3c8c9ed-fbab-438a-b731-bb0ddc048e50</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329351/C%C3%A0_ri_b%C3%A1nh_m%C3%AC_monchinh_qxnsxv.png</t>
   </si>
   <si>
     <t>NẤm lÚC LẮC KHOAI TÂY</t>
@@ -561,7 +561,7 @@
     <t>Stir-fried Water Spinach with Garlic</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151896/IMG_3752_obk7fm.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329703/IMG_3753_w7bocz.jpg</t>
   </si>
   <si>
     <t>RAU MUỐNG XÀO NẤM</t>
@@ -573,7 +573,7 @@
     <t>Stir-fried Water Spinach with Mushrooms</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151912/IMG_3989_yaeqvc.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329929/IMG_3995_ioo3au.jpg</t>
   </si>
   <si>
     <t>RAU XÀO THẬP CẨM</t>
@@ -621,7 +621,7 @@
     <t>Stir-fried Mushroom with Black Pepper Sauce</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monman%2FNa%CC%82%CC%81m%20so%CC%82%CC%81t%20tie%CC%82u%20%C4%91en_monman.jpg?alt=media&amp;token=c51fc7f0-559e-439d-bc5f-9a498a039977</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329705/IMG_3762_tfx6lp.jpg</t>
   </si>
   <si>
     <t>ĐẬU HỦ SỐT TỨ XUYÊN</t>
@@ -633,7 +633,7 @@
     <t>Mapo Tofu</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151897/IMG_3730_vh01tt.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329702/IMG_3730_xjbdx1.jpg</t>
   </si>
   <si>
     <t>ĐẬU HỦ CHƯNG TƯƠNG</t>
@@ -642,7 +642,7 @@
     <t>Steamed Tofu with Salted Soybean Sauce</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151897/IMG_3762_zqt1wz.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329359/%C4%90%E1%BA%ADu_h%C5%A9_ch%C6%B0ng_t%C6%B0%C6%A1ng_monman_pu2qsi.png</t>
   </si>
   <si>
     <t>ĐẬU HỦ XỐC SA TẾ</t>
@@ -654,7 +654,7 @@
     <t>Satay Tofu</t>
   </si>
   <si>
-    <t>https://firebasestorage.googleapis.com/v0/b/dieuthien-production.appspot.com/o/monman%2F%C4%90a%CC%A3%CC%82u%20hu%CC%83%20xo%CC%82%CC%81c%20sa%20te%CC%82%CC%81_monman.jpg?alt=media&amp;token=65951195-23c9-48f6-b738-618a4cbaf70a</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329320/%C4%90%E1%BA%ADu_h%C5%A9_x%E1%BB%91c_sa_t%E1%BA%BF_monman_1_obiolm.png</t>
   </si>
   <si>
     <t>NẤM RƠM KHO TIÊU</t>
@@ -723,7 +723,7 @@
     <t>được nấu từ sữa đậu nành nguyên chất , gelatin dùng kèm với cái loại mức trái cây</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780151911/IMG_3983_mhs5br.jpg</t>
+    <t>https://res.cloudinary.com/dix539uvo/image/upload/v1780329706/IMG_3983_hjeyh1.jpg</t>
   </si>
   <si>
     <t>Image_preview</t>
@@ -3144,7 +3144,7 @@
 "),"黄面条、甜椒、大白菜、洋葱、小白菜、炸豆腐、炸蘑菇、炸红葱头。")</f>
         <v>黄面条、甜椒、大白菜、洋葱、小白菜、炸豆腐、炸蘑菇、炸红葱头。</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="9" t="s">
         <v>146</v>
       </c>
       <c r="J35" s="10" t="b">
@@ -3760,7 +3760,7 @@
 "),"杏鲍菇和黑胡椒酱")</f>
         <v>杏鲍菇和黑胡椒酱</v>
       </c>
-      <c r="I49" s="16" t="s">
+      <c r="I49" s="9" t="s">
         <v>201</v>
       </c>
       <c r="J49" s="10" t="b">
@@ -3892,7 +3892,7 @@
 "),"炸豆腐、洋葱、甜椒、沙爹酱")</f>
         <v>炸豆腐、洋葱、甜椒、沙爹酱</v>
       </c>
-      <c r="I52" s="16" t="s">
+      <c r="I52" s="9" t="s">
         <v>212</v>
       </c>
       <c r="J52" s="10" t="b">
